--- a/artfynd/A 54492-2024 artfynd.xlsx
+++ b/artfynd/A 54492-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65817320</v>
+        <v>65817322</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668135.3076323934</v>
+        <v>668071</v>
       </c>
       <c r="R2" t="n">
-        <v>6662274.416819096</v>
+        <v>6662283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2017-04-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-04-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca. 1 dm2 på levande hasselstam, omkr. 28 cm.</t>
+          <t>1 ex. på död, stående hassel, omkr. 8 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +783,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Levande hasselstam. # Hassel</t>
+          <t>Död, stående hassel. # Hassel</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65817322</v>
+        <v>65817324</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>3929</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668070.814165666</v>
+        <v>668094</v>
       </c>
       <c r="R3" t="n">
-        <v>6662282.967131811</v>
+        <v>6662282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,24 +878,14 @@
           <t>2017-04-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-04-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex. på död, stående hassel, omkr. 8 cm.</t>
+          <t>13 ex. på död stående hassel, omkr. 17 cm.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -957,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65817324</v>
+        <v>65817320</v>
       </c>
       <c r="B4" t="n">
-        <v>79764</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,31 +938,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3929</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1006,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668093.8941614598</v>
+        <v>668135</v>
       </c>
       <c r="R4" t="n">
-        <v>6662282.02243673</v>
+        <v>6662274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,24 +1004,14 @@
           <t>2017-04-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-04-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex. på död stående hassel, omkr. 17 cm.</t>
+          <t>Ca. 1 dm2 på levande hasselstam, omkr. 28 cm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,7 +1035,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Död, stående hassel. # Hassel</t>
+          <t>Levande hasselstam. # Hassel</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1098,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75553352</v>
+        <v>75553350</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668060.7883142515</v>
+        <v>668119</v>
       </c>
       <c r="R5" t="n">
-        <v>6662327.005058631</v>
+        <v>6662304</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1171,19 +1121,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,27 +1138,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75553350</v>
+        <v>75553351</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668118.923263896</v>
+        <v>668081</v>
       </c>
       <c r="R6" t="n">
-        <v>6662304.165177527</v>
+        <v>6662312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,19 +1218,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,27 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75553351</v>
+        <v>75553352</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668081.0084299811</v>
+        <v>668061</v>
       </c>
       <c r="R7" t="n">
-        <v>6662311.9308246</v>
+        <v>6662327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,19 +1315,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
